--- a/data/mentors.template.xlsx
+++ b/data/mentors.template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mentors" sheetId="1" r:id="R6284aa1c5d2e4cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mentors" sheetId="1" r:id="R09177e9065ad45e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,25 +20,25 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="16"/>
+      <x:sz val="20"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF754458"/>
+      <x:color rgb="FF7A4B60"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13"/>
+      <x:sz val="16"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
-      <x:color rgb="FF754E5E"/>
+      <x:color rgb="FF7A4B60"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -56,201 +56,85 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFBE0EA"/>
+        <x:fgColor rgb="FFFCE1EB"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF8BB25"/>
+        <x:fgColor rgb="FFFFC52B"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF7E6"/>
+        <x:fgColor rgb="FFFFF8E9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="19">
+  <x:borders count="6">
     <x:border/>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0B8CA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFF0B8CA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF0B8CA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF0B8CA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF6D2DD"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFF6D2DD"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF6D2DD"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF6D2DD"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF0D799"/>
       </x:left>
       <x:top style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:right style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFEAA9C0"/>
+        <x:color rgb="FFF0D799"/>
       </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFF1C8D6"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFF0DBA4"/>
-      </x:top>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -263,48 +147,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -314,67 +164,25 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -579,110 +387,136 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" ht="44" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>東海の日 プロフィール帳：メンター登録シート</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>mentorId</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="9" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="9" t="str">
         <x:v>generation</x:v>
       </x:c>
-      <x:c r="D3" s="15" t="str">
+      <x:c r="D3" s="9" t="str">
+        <x:v>iconUrl</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str">
         <x:v>imageUrl</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="22" t="str">
+      <x:c r="A4" s="11" t="str">
         <x:v>syokora</x:v>
       </x:c>
-      <x:c r="B4" s="23" t="str">
+      <x:c r="B4" s="11" t="str">
         <x:v>ショコラ</x:v>
       </x:c>
-      <x:c r="C4" s="23" t="str">
+      <x:c r="C4" s="11" t="str">
         <x:v>18期</x:v>
       </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>https://example.com/images/syokora.png</x:v>
+      <x:c r="D4" s="11" t="str">
+        <x:v>https://example.com/icons/syokora.jpg</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>https://example.com/profiles/syokora.png</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="25" t="str">
+      <x:c r="A5" s="11" t="str">
         <x:v>tarou</x:v>
       </x:c>
-      <x:c r="B5" s="26" t="str">
+      <x:c r="B5" s="11" t="str">
         <x:v>タロウ</x:v>
       </x:c>
-      <x:c r="C5" s="26" t="str">
+      <x:c r="C5" s="11" t="str">
         <x:v>OB・OG</x:v>
       </x:c>
-      <x:c r="D5" s="27" t="str">
-        <x:v>https://example.com/images/tarou.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="30" t="str">
+      <x:c r="D5" s="11" t="str">
+        <x:v>https://example.com/icons/tarou.jpg</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>https://example.com/profiles/tarou.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="14" t="str">
         <x:v>入力ルール</x:v>
       </x:c>
-      <x:c r="B7" s="30"/>
-      <x:c r="C7" s="30"/>
-      <x:c r="D7" s="30"/>
-    </x:row>
-    <x:row r="8" ht="33" customHeight="1">
-      <x:c r="A8" s="51" t="str">
+      <x:c r="B7" s="14"/>
+      <x:c r="C7" s="14"/>
+      <x:c r="D7" s="14"/>
+      <x:c r="E7" s="14"/>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="23" t="str">
         <x:v>• mentorId：半角英数字・ハイフン・アンダースコアのみ。登録後は変更しない。</x:v>
       </x:c>
-      <x:c r="B8" s="52"/>
-      <x:c r="C8" s="52"/>
-      <x:c r="D8" s="53"/>
-    </x:row>
-    <x:row r="9" ht="33" customHeight="1">
-      <x:c r="A9" s="54" t="str">
-        <x:v>• imageUrl：HTTPSで公開できるプロフィール画像URL。</x:v>
-      </x:c>
-      <x:c r="B9" s="55"/>
-      <x:c r="C9" s="55"/>
-      <x:c r="D9" s="56"/>
-    </x:row>
-    <x:row r="10" ht="33" customHeight="1">
-      <x:c r="A10" s="54" t="str">
-        <x:v>• QRは初回の一括登録で人数分を未割当のまま発行する。Excelには入力不要で、配布はランダムでOK。</x:v>
-      </x:c>
-      <x:c r="B10" s="55"/>
-      <x:c r="C10" s="55"/>
-      <x:c r="D10" s="56"/>
-    </x:row>
-    <x:row r="11" ht="33" customHeight="1">
-      <x:c r="A11" s="57" t="str">
+      <x:c r="B8" s="24"/>
+      <x:c r="C8" s="24"/>
+      <x:c r="D8" s="24"/>
+      <x:c r="E8" s="25"/>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="23" t="str">
+        <x:v>• iconUrl：一覧用の顔アイコンURL。HTTPSの正方形に近い顔写真を推奨。</x:v>
+      </x:c>
+      <x:c r="B9" s="24"/>
+      <x:c r="C9" s="24"/>
+      <x:c r="D9" s="24"/>
+      <x:c r="E9" s="25"/>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="23" t="str">
+        <x:v>• imageUrl：QR獲得時にポップアップ表示するプロフィール帳用画像のHTTPS URL。</x:v>
+      </x:c>
+      <x:c r="B10" s="24"/>
+      <x:c r="C10" s="24"/>
+      <x:c r="D10" s="24"/>
+      <x:c r="E10" s="25"/>
+    </x:row>
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="23" t="str">
+        <x:v>• QRは初回の一括登録で人数分を未割当のまま発行する。Excelには入力不要、配布はランダムでOK。</x:v>
+      </x:c>
+      <x:c r="B11" s="24"/>
+      <x:c r="C11" s="24"/>
+      <x:c r="D11" s="24"/>
+      <x:c r="E11" s="25"/>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="23" t="str">
         <x:v>• 3行目の見出しは変更せず、4行目以降のサンプルを差し替えて使う。</x:v>
       </x:c>
-      <x:c r="B11" s="58"/>
-      <x:c r="C11" s="58"/>
-      <x:c r="D11" s="59"/>
+      <x:c r="B12" s="24"/>
+      <x:c r="C12" s="24"/>
+      <x:c r="D12" s="24"/>
+      <x:c r="E12" s="25"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A7:D7"/>
-    <x:mergeCell ref="A8:D8"/>
-    <x:mergeCell ref="A9:D9"/>
-    <x:mergeCell ref="A10:D10"/>
-    <x:mergeCell ref="A11:D11"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A7:E7"/>
+    <x:mergeCell ref="A8:E8"/>
+    <x:mergeCell ref="A9:E9"/>
+    <x:mergeCell ref="A10:E10"/>
+    <x:mergeCell ref="A11:E11"/>
+    <x:mergeCell ref="A12:E12"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/mentors.template.xlsx
+++ b/data/mentors.template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mentors" sheetId="1" r:id="R09177e9065ad45e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mentors" sheetId="1" r:id="Rb1b495c2974b42f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +41,36 @@
       <x:color rgb="FF7A4B60"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF75435A"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF75435A"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,8 +97,48 @@
         <x:fgColor rgb="FFFFF8E9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7548B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE0EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFC72C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7548B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE0EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFC72C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -130,11 +198,53 @@
         <x:color rgb="FFF0D799"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF4B5CA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFF4B5CA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF4B5CA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF4B5CA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF7C3D4"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFF7C3D4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF7C3D4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF7C3D4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF6D38C"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFF6D38C"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF6D38C"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF6D38C"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="67">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -185,11 +295,129 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -387,137 +615,181 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="44" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+    <x:row r="1" ht="48" customHeight="1">
+      <x:c r="A1" s="54" t="str">
         <x:v>東海の日 プロフィール帳：メンター登録シート</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="9" t="str">
+      <x:c r="B1" s="54"/>
+      <x:c r="C1" s="54"/>
+      <x:c r="D1" s="54"/>
+      <x:c r="E1"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="59" t="str">
         <x:v>mentorId</x:v>
       </x:c>
-      <x:c r="B3" s="9" t="str">
+      <x:c r="B3" s="59" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="str">
+      <x:c r="C3" s="59" t="str">
         <x:v>generation</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="str">
-        <x:v>iconUrl</x:v>
-      </x:c>
-      <x:c r="E3" s="9" t="str">
-        <x:v>imageUrl</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="11" t="str">
+      <x:c r="D3" s="59" t="str">
+        <x:v>isOpenFromStart</x:v>
+      </x:c>
+      <x:c r="E3"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="40" t="str">
         <x:v>syokora</x:v>
       </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="B4" s="40" t="str">
         <x:v>ショコラ</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="str">
+      <x:c r="C4" s="40" t="str">
         <x:v>18期</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>https://example.com/icons/syokora.jpg</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str">
-        <x:v>https://example.com/profiles/syokora.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="D4" s="50" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="E4"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="40" t="str">
         <x:v>tarou</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="B5" s="40" t="str">
         <x:v>タロウ</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="str">
+      <x:c r="C5" s="40" t="str">
         <x:v>OB・OG</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>https://example.com/icons/tarou.jpg</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>https://example.com/profiles/tarou.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="D5" s="50" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="E5"/>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="62" t="str">
         <x:v>入力ルール</x:v>
       </x:c>
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="14"/>
-      <x:c r="D7" s="14"/>
-      <x:c r="E7" s="14"/>
+      <x:c r="B7" s="62"/>
+      <x:c r="C7" s="62"/>
+      <x:c r="D7" s="62"/>
+      <x:c r="E7"/>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="23" t="str">
+      <x:c r="A8" s="66" t="str">
         <x:v>• mentorId：半角英数字・ハイフン・アンダースコアのみ。登録後は変更しない。</x:v>
       </x:c>
-      <x:c r="B8" s="24"/>
-      <x:c r="C8" s="24"/>
-      <x:c r="D8" s="24"/>
-      <x:c r="E8" s="25"/>
+      <x:c r="B8" s="66" t="str">
+        <x:v>• mentorId：半角英数字・ハイフン・アンダースコアのみ。登録後は変更しない。</x:v>
+      </x:c>
+      <x:c r="C8" s="66" t="str">
+        <x:v>• mentorId：半角英数字・ハイフン・アンダースコアのみ。登録後は変更しない。</x:v>
+      </x:c>
+      <x:c r="D8" s="66" t="str">
+        <x:v>• mentorId：半角英数字・ハイフン・アンダースコアのみ。登録後は変更しない。</x:v>
+      </x:c>
+      <x:c r="E8"/>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="23" t="str">
-        <x:v>• iconUrl：一覧用の顔アイコンURL。HTTPSの正方形に近い顔写真を推奨。</x:v>
-      </x:c>
-      <x:c r="B9" s="24"/>
-      <x:c r="C9" s="24"/>
-      <x:c r="D9" s="24"/>
-      <x:c r="E9" s="25"/>
+      <x:c r="A9" s="66" t="str">
+        <x:v>• name：表示名。data/mentor-images 内の画像ファイル名にも、この名前を含める。</x:v>
+      </x:c>
+      <x:c r="B9" s="66" t="str">
+        <x:v>• name：表示名。data/mentor-images 内の画像ファイル名にも、この名前を含める。</x:v>
+      </x:c>
+      <x:c r="C9" s="66" t="str">
+        <x:v>• name：表示名。data/mentor-images 内の画像ファイル名にも、この名前を含める。</x:v>
+      </x:c>
+      <x:c r="D9" s="66" t="str">
+        <x:v>• name：表示名。data/mentor-images 内の画像ファイル名にも、この名前を含める。</x:v>
+      </x:c>
+      <x:c r="E9"/>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="23" t="str">
-        <x:v>• imageUrl：QR獲得時にポップアップ表示するプロフィール帳用画像のHTTPS URL。</x:v>
-      </x:c>
-      <x:c r="B10" s="24"/>
-      <x:c r="C10" s="24"/>
-      <x:c r="D10" s="24"/>
-      <x:c r="E10" s="25"/>
+      <x:c r="A10" s="66" t="str">
+        <x:v>• isOpenFromStart：当日不参加など、開始時から閲覧可能にする人だけ true。空欄・false はQR獲得後に公開。</x:v>
+      </x:c>
+      <x:c r="B10" s="66" t="str">
+        <x:v>• isOpenFromStart：当日不参加など、開始時から閲覧可能にする人だけ true。空欄・false はQR獲得後に公開。</x:v>
+      </x:c>
+      <x:c r="C10" s="66" t="str">
+        <x:v>• isOpenFromStart：当日不参加など、開始時から閲覧可能にする人だけ true。空欄・false はQR獲得後に公開。</x:v>
+      </x:c>
+      <x:c r="D10" s="66" t="str">
+        <x:v>• isOpenFromStart：当日不参加など、開始時から閲覧可能にする人だけ true。空欄・false はQR獲得後に公開。</x:v>
+      </x:c>
+      <x:c r="E10"/>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="23" t="str">
-        <x:v>• QRは初回の一括登録で人数分を未割当のまま発行する。Excelには入力不要、配布はランダムでOK。</x:v>
-      </x:c>
-      <x:c r="B11" s="24"/>
-      <x:c r="C11" s="24"/>
-      <x:c r="D11" s="24"/>
-      <x:c r="E11" s="25"/>
+      <x:c r="A11" s="66" t="str">
+        <x:v>• 画像は ショコラ_icon.jpg / ショコラ_profile.jpg のように置く。ショコラ.jpg 1枚なら両方に使う。</x:v>
+      </x:c>
+      <x:c r="B11" s="66" t="str">
+        <x:v>• 画像は ショコラ_icon.jpg / ショコラ_profile.jpg のように置く。ショコラ.jpg 1枚なら両方に使う。</x:v>
+      </x:c>
+      <x:c r="C11" s="66" t="str">
+        <x:v>• 画像は ショコラ_icon.jpg / ショコラ_profile.jpg のように置く。ショコラ.jpg 1枚なら両方に使う。</x:v>
+      </x:c>
+      <x:c r="D11" s="66" t="str">
+        <x:v>• 画像は ショコラ_icon.jpg / ショコラ_profile.jpg のように置く。ショコラ.jpg 1枚なら両方に使う。</x:v>
+      </x:c>
+      <x:c r="E11"/>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="66" t="str">
+        <x:v>• QRは初回の一括登録で未割当のまま発行する。Excelには入力不要、配布はランダムでOK。</x:v>
+      </x:c>
+      <x:c r="B12" s="66" t="str">
+        <x:v>• QRは初回の一括登録で未割当のまま発行する。Excelには入力不要、配布はランダムでOK。</x:v>
+      </x:c>
+      <x:c r="C12" s="66" t="str">
+        <x:v>• QRは初回の一括登録で未割当のまま発行する。Excelには入力不要、配布はランダムでOK。</x:v>
+      </x:c>
+      <x:c r="D12" s="66" t="str">
+        <x:v>• QRは初回の一括登録で未割当のまま発行する。Excelには入力不要、配布はランダムでOK。</x:v>
+      </x:c>
+      <x:c r="E12"/>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="66" t="str">
         <x:v>• 3行目の見出しは変更せず、4行目以降のサンプルを差し替えて使う。</x:v>
       </x:c>
-      <x:c r="B12" s="24"/>
-      <x:c r="C12" s="24"/>
-      <x:c r="D12" s="24"/>
-      <x:c r="E12" s="25"/>
+      <x:c r="B13" s="66" t="str">
+        <x:v>• 3行目の見出しは変更せず、4行目以降のサンプルを差し替えて使う。</x:v>
+      </x:c>
+      <x:c r="C13" s="66" t="str">
+        <x:v>• 3行目の見出しは変更せず、4行目以降のサンプルを差し替えて使う。</x:v>
+      </x:c>
+      <x:c r="D13" s="66" t="str">
+        <x:v>• 3行目の見出しは変更せず、4行目以降のサンプルを差し替えて使う。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A7:E7"/>
-    <x:mergeCell ref="A8:E8"/>
-    <x:mergeCell ref="A9:E9"/>
-    <x:mergeCell ref="A10:E10"/>
-    <x:mergeCell ref="A11:E11"/>
-    <x:mergeCell ref="A12:E12"/>
+    <x:mergeCell ref="A13:D13"/>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A7:D7"/>
+    <x:mergeCell ref="A8:D8"/>
+    <x:mergeCell ref="A9:D9"/>
+    <x:mergeCell ref="A10:D10"/>
+    <x:mergeCell ref="A11:D11"/>
+    <x:mergeCell ref="A12:D12"/>
   </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="D4:D200">
+      <x:formula1>"true,false"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>